--- a/site/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Candidates</t>
+          <t>Manage Workers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K4W4EFX81YEQ52GB2ZS3J422</t>
+          <t>h_01KP8BKERMEF8PMPXBA3EB6QTT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K4W4EFX81YEQ52GB2ZS3J422</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP8BKERMEF8PMPXBA3EB6QTT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Workers</t>
+          <t>Correlation and Filters</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K997TH2H98G126J9D2C4BH5P</t>
+          <t>h_01KP8BKERM9BKXCRT6SBHE1RX7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K997TH2H98G126J9D2C4BH5P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP8BKERM9BKXCRT6SBHE1RX7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation and Filters</t>
+          <t>ADP Workforce Now Workers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K997YCN7PX0MWE7W57CEVR4H</t>
+          <t>h_01KP8BN5DM7REW6Q88042RFCC3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K997YCN7PX0MWE7W57CEVR4H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP8BN5DM7REW6Q88042RFCC3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Naming Policy</t>
+          <t>Manage Candidates</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K94HJ4VRD3Z51KDD0GHGF1AR</t>
+          <t>h_01K4W4EFX81YEQ52GB2ZS3J422</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K94HJ4VRD3Z51KDD0GHGF1AR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K4W4EFX81YEQ52GB2ZS3J422</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Correlation and Filters</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K973S8HT3RKTMNDDBW21XRHS</t>
+          <t>h_01KP851H3TQ68V23225211N81Q</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01K973S8HT3RKTMNDDBW21XRHS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP851H3TQ68V23225211N81Q</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Writeback to ADP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+          <t>h_01KP85D87JVNDS6HP1F0TV4CYE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85D87JVNDS6HP1F0TV4CYE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Writeback to ADP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01JZ7GJ97ZX233WAF2MGX9PFME</t>
+          <t>h_01KP85DSNS2P6H7X9WT218YC8S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01JZ7GJ97ZX233WAF2MGX9PFME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85DSNS2P6H7X9WT218YC8S</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Deprovisioning Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,144 +825,1046 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5XVFZRJYTGXBGXBVCAGA4HN</t>
+          <t>h_01KP85GT2S9Q7APWYS9J1K6NX8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01K5XVFZRJYTGXBGXBVCAGA4HN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85GT2S9Q7APWYS9J1K6NX8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Deprovisioning Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K5TEHNZK8ZQ1P48ZQSRAR19M</t>
+          <t>h_01KP85GXS099DX5NBYRB8KYSDT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K5TEHNZK8ZQ1P48ZQSRAR19M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85GXS099DX5NBYRB8KYSDT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>AD Group Sync</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KP85MHTJEREGJ1CJKQMMHFYR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85MHTJEREGJ1CJKQMMHFYR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Active Directory Group Assignment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KP85MMWZJA605VFPBWKPX05V</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85MMWZJA605VFPBWKPX05V</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>User Update</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KP85R0MX1CSNEBD41XVS0XCP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85R0MX1CSNEBD41XVS0XCP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Update AD Account Identifiers on Candidate Name Change</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KP85QXKFEFD632C9W5RE3J1K</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85QXKFEFD632C9W5RE3J1K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Update AD Account Identifiers on Worker Conversion</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KP85V5VZSFDXFGZKYF0F14MB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85V5VZSFDXFGZKYF0F14MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KP85Z4PS7SKK87GP93J6J9ZJ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85Z4PS7SKK87GP93J6J9ZJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Password Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KP85Z2AVY3FMSSPTYZ0BWW7N</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP85Z2AVY3FMSSPTYZ0BWW7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KP862KC9208BD8SYBVX1T4T4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP862KC9208BD8SYBVX1T4T4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KP862REBBE4A1JR9Y9V77X4T</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP862REBBE4A1JR9Y9V77X4T</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Naming Policy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KP864F184PNEDKVYQJMD31J6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP864F184PNEDKVYQJMD31J6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Generate ProxyAddress (proxyAddress)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KP86BR591ZXXKRR0C4K15DRA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86BR591ZXXKRR0C4K15DRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UPN &amp; Email Domain Management</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KP86CTBH3AJQA017TM6GWAMG</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86CTBH3AJQA017TM6GWAMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KP86ED9Q19Z87BKVS17ZNB1W</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86ED9Q19Z87BKVS17ZNB1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KP8AS967EB3QCXM4G45ZFT9P</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP8AS967EB3QCXM4G45ZFT9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KP86EG3V7MMV2YC43A2QN75D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86EG3V7MMV2YC43A2QN75D</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Reporting Settings</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KP86FPARSA7D0G0QNTSAWAP1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86FPARSA7D0G0QNTSAWAP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Insights Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KP86HP2X39C5DXPZ4D2MPJCY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86HP2X39C5DXPZ4D2MPJCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KP86HS7ENYAH4Q6ENXE2CZXS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86HS7ENYAH4Q6ENXE2CZXS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KP86K4WWWP99FY51VFM23H9G</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86K4WWWP99FY51VFM23H9G</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KP86K26YPM4HSS3P8M977W3E</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86K26YPM4HSS3P8M977W3E</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Success Execution</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KP86ZS3RNW9JMKBSFH2BT57K</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP86ZS3RNW9JMKBSFH2BT57K</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Failure Execution</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KP8720J8HY7RXR7SNBSVNHKM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP8720J8HY7RXR7SNBSVNHKM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Candidate Rules</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KP88FBCY0DQKMXG4TY0YQWRK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88FBCY0DQKMXG4TY0YQWRK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Candidate Group Rules</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KP88FREK4H701PP9PV0TEHX0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88FREK4H701PP9PV0TEHX0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OU Rules</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KP88G7VEG9QR4E66ADTHSSQR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88G7VEG9QR4E66ADTHSSQR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OU Rules</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KP88GJ54SB78KWQVWP7VRE1T</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88GJ54SB78KWQVWP7VRE1T</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KP88CAHDZ9WEDWXXYQH8NP0V</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88CAHDZ9WEDWXXYQH8NP0V</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Candidate Map</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KP88CTYZRBXSBZR2ZEJMMAQM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88CTYZRBXSBZR2ZEJMMAQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Monitored Provisioning</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KP88FBCYXHF53P53XYCAC9E5</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KP88FBCYXHF53P53XYCAC9E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Manage Workers</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>h_01K997TH2H98G126J9D2C4BH5P</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K997TH2H98G126J9D2C4BH5P</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Correlation and Filters</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01K997YCN7PX0MWE7W57CEVR4H</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K997YCN7PX0MWE7W57CEVR4H</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Naming Policy</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01K94HJ4VRD3Z51KDD0GHGF1AR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K94HJ4VRD3Z51KDD0GHGF1AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>01K973S8HT3RKTMNDDBW21XRHS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01K973S8HT3RKTMNDDBW21XRHS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01K5RAXMQQAWTTT5GM0YKX2RKZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01JZ7GJ97ZX233WAF2MGX9PFME</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01JZ7GJ97ZX233WAF2MGX9PFME</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>01KP8ASZ9VEC7XE11R8YRQGPPQ</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01KP8ASZ9VEC7XE11R8YRQGPPQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01K5TEHNZK8ZQ1P48ZQSRAR19M</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K5TEHNZK8ZQ1P48ZQSRAR19M</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>01KP886NBVC06F5CEEKNT7J61W</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01KP886NBVC06F5CEEKNT7J61W</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>01KP886NBVN6XV0B5MM3VGBQX0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-Integration-Guide/#01KP886NBVN6XV0B5MM3VGBQX0</t>
         </is>
       </c>
     </row>
